--- a/Config/Excel/skill/skill.xlsx
+++ b/Config/Excel/skill/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
   <si>
     <t>id</t>
   </si>
@@ -37,13 +37,19 @@
     <t>targetRule</t>
   </si>
   <si>
-    <t>abilityId</t>
-  </si>
-  <si>
     <t>cost</t>
   </si>
   <si>
     <t>view</t>
+  </si>
+  <si>
+    <t>abilityId</t>
+  </si>
+  <si>
+    <t>hitFormula</t>
+  </si>
+  <si>
+    <t>hitModification</t>
   </si>
   <si>
     <t>c</t>
@@ -995,18 +1001,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="16.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1022,67 +1030,91 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>100000</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="F5" s="1">
         <v>110000</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/skill/skill.xlsx
+++ b/Config/Excel/skill/skill.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\demo\Project001\Config\Excel\skill\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -29,11 +34,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>targetRule</t>
   </si>
   <si>
@@ -46,10 +57,13 @@
     <t>abilityId</t>
   </si>
   <si>
-    <t>hitFormula</t>
-  </si>
-  <si>
-    <t>hitModification</t>
+    <t>hitMdf</t>
+  </si>
+  <si>
+    <t>criticalMdf</t>
+  </si>
+  <si>
+    <t>criticalDamageMdf</t>
   </si>
   <si>
     <t>c</t>
@@ -62,6 +76,27 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>目标规则</t>
+  </si>
+  <si>
+    <t>能力</t>
+  </si>
+  <si>
+    <t>命中修正（-1：必定命中）</t>
+  </si>
+  <si>
+    <t>暴击率修正（-1：必定暴击；-2：必不暴击）</t>
+  </si>
+  <si>
+    <t>暴击伤害修正</t>
   </si>
 </sst>
 </file>
@@ -1001,20 +1036,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="16.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="1" customWidth="1"/>
+    <col min="2" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1036,84 +1072,132 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:11">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>100000</v>
       </c>
-      <c r="C5" s="1">
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>110000</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K5" s="1">
         <v>10000</v>
       </c>
     </row>
